--- a/satisfaction_surveys/004_men_s_grooming_preference_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/004_men_s_grooming_preference_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>men_s_grooming_preference_survey</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>hair_haircut_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>How often do you get a hair cut?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hair_haircut_style</t>
+          <t>beard_maintenance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hair_haircut_style</t>
+          <t>How do you maintain your beard?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency</t>
+          <t>What skincare products do you use?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>beard_maintenance</t>
+          <t>shaving</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>beard_maintenance</t>
+          <t>How often do you shave?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>beard_maintenance_frequency</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>beard_maintenance_frequency</t>
+          <t>Do you use fragrances?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>skincare_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>How often do you apply skincare?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>skincare_frequency</t>
+          <t>skincare_tools</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>skincare_frequency</t>
+          <t>What skincare tools do you use?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shaving</t>
+          <t>skincare_product</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shaving</t>
+          <t>What type of skincare product do you use?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>shaving_frequency</t>
+          <t>haircut_cost</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shaving_frequency</t>
+          <t>How much do you spend on haircuts?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>skincare_price</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>How much do you spend on skincare?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fragrance_frequency</t>
+          <t>hair_haircut</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fragrance_frequency</t>
+          <t>What type of hair cut do you get?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>skincare_product</t>
+          <t>hair_haircut_frequency_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>skincare_product</t>
+          <t>Hair Haircut Frequency 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>skincare_price</t>
+          <t>hair_haircut_brand</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>skincare_price</t>
+          <t>What brand of hair cut do you use?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hair_haircut_cost</t>
+          <t>skincare_brand</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hair_haircut_cost</t>
+          <t>What brand of skincare do you use?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>skincare_tools</t>
+          <t>hair_haircut_size</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>skincare_tools</t>
+          <t>What size of hair cut do you get?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>beard_tools</t>
+          <t>hair_haircut_form</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>beard_tools</t>
+          <t>What form of hair cut do you get?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>skincare_brand</t>
+          <t>skincare_size</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>skincare_brand</t>
+          <t>What size of skincare do you use?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hair_haircut_brand</t>
+          <t>skincare_size_form</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>hair_haircut_brand</t>
+          <t>What form of skincare do you use?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>skincare_haircut</t>
+          <t>skincare_product_size</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>skincare_haircut</t>
+          <t>Skincare Product Size</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency</t>
+          <t>skincare_product_form</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency</t>
+          <t>Skincare Product Form</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>skincare_product_size</t>
+          <t>skincare_characteristics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>skincare_product_size</t>
+          <t>What characteristics of skincare do you look for?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>skincare_product_type</t>
+          <t>skincare_characteristics_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>skincare_product_size</t>
+          <t>What other characteristics of skincare do you look for?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,17 +1044,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>skincare_product_form</t>
+          <t>skincare_characteristics_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>skincare_product_form</t>
+          <t>Skincare Characteristics 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,21 +1067,182 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>skincare_product_size_form</t>
+          <t>open_question_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>skincare_product_size</t>
+          <t>Can you tell us anything else about your skincare habits?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>open_question_2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your haircut habits?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>open_question_3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your skin types?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>open_question_4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your skincare product frequency?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>open_question_5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your skincare brand?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>open_question_6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your haircut frequency?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>open_question_7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your haircut size?</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>open_question_8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Can you tell us anything else about your haircut brand?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +1259,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,374 +1287,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hair_haircut_style_choices</t>
+          <t>hair_haircut_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>beard</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beard</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hair_haircut_style_choices</t>
+          <t>hair_haircut_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bald</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bald</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hair_haircut_style_choices</t>
+          <t>hair_haircut_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>crew</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crew</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hair_haircut_style_choices</t>
+          <t>hair_haircut_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pompadour</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pompadour</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hair_haircut_style_choices</t>
+          <t>beard_maintenance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fade</t>
+          <t>trims</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fade</t>
+          <t>Trims</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hair_haircut_style_choices</t>
+          <t>beard_maintenance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quiff</t>
+          <t>oils</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quiff</t>
+          <t>Oils</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>beard_maintenance_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>waxes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>Waxes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>beard_maintenance_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>skincare_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>cleanser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Cleanser</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>skincare_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>moisturiser</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Moisturiser</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>beard_maintenance_choices</t>
+          <t>skincare_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trims</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trims</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beard_maintenance_choices</t>
+          <t>skincare_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>oils</t>
+          <t>sunscreen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oils</t>
+          <t>Sunscreen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>beard_maintenance_choices</t>
+          <t>shaving_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>waxes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Waxes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>beard_maintenance_choices</t>
+          <t>shaving_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>beard_maintenance_frequency_choices</t>
+          <t>shaving_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>beard_maintenance_frequency_choices</t>
+          <t>shaving_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>beard_maintenance_frequency_choices</t>
+          <t>fragrance_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>beard_maintenance_frequency_choices</t>
+          <t>fragrance_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>skincare_choices</t>
+          <t>fragrance_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cleanser</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleanser</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>skincare_choices</t>
+          <t>fragrance_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>moisturiser</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Moisturiser</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>skincare_choices</t>
+          <t>skincare_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>serum</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>skincare_choices</t>
+          <t>skincare_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sunscreen</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sunscreen</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1666,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -1522,1185 +1683,1066 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>skincare_frequency_choices</t>
+          <t>skincare_tools_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>razors</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>Razors</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>skincare_frequency_choices</t>
+          <t>skincare_tools_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>clippers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Clippers</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>shaving_choices</t>
+          <t>skincare_tools_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>trimmers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Trimmers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shaving_choices</t>
+          <t>skincare_tools_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>brushes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>Brushes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>shaving_choices</t>
+          <t>skincare_tools_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>shaving_choices</t>
+          <t>haircut_cost_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_$10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than $10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>shaving_frequency_choices</t>
+          <t>haircut_cost_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>$10-$20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>$10-$20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>shaving_frequency_choices</t>
+          <t>haircut_cost_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>$21-$30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>$21-$30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>shaving_frequency_choices</t>
+          <t>haircut_cost_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>$31_or_more</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>$31 or more</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fragrance_choices</t>
+          <t>skincare_price_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>less_than_$10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Less than $10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fragrance_choices</t>
+          <t>skincare_price_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>$10-$20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>$10-$20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fragrance_choices</t>
+          <t>skincare_price_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>$21-$30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>$21-$30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fragrance_choices</t>
+          <t>skincare_price_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>$31_or_more</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>$31 or more</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fragrance_frequency_choices</t>
+          <t>hair_haircut_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fragrance_frequency_choices</t>
+          <t>hair_haircut_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>p</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fragrance_frequency_choices</t>
+          <t>hair_haircut_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fragrance_frequency_choices</t>
+          <t>hair_haircut_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>k</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>K</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>skincare_price_choices</t>
+          <t>hair_haircut_frequency_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>less_than_$10</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Less than $10</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>skincare_price_choices</t>
+          <t>hair_haircut_frequency_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>$10-$20</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$10-$20</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>skincare_price_choices</t>
+          <t>hair_haircut_frequency_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>$21-$30</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$21-$30</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>skincare_price_choices</t>
+          <t>hair_haircut_frequency_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>$31_or_more</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>$31 or more</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hair_haircut_cost_choices</t>
+          <t>hair_haircut_brand_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>less_than_$10</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Less than $10</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hair_haircut_cost_choices</t>
+          <t>hair_haircut_brand_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>$10-$20</t>
+          <t>p</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>$10-$20</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hair_haircut_cost_choices</t>
+          <t>hair_haircut_brand_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>$21-$30</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$21-$30</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hair_haircut_cost_choices</t>
+          <t>hair_haircut_brand_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>$31_or_more</t>
+          <t>k</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$31 or more</t>
+          <t>K</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>skincare_tools_choices</t>
+          <t>skincare_brand_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>razors</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Razors</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>skincare_tools_choices</t>
+          <t>skincare_brand_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>clippers</t>
+          <t>p</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>skincare_tools_choices</t>
+          <t>skincare_brand_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>trimmers</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Trimmers</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>skincare_tools_choices</t>
+          <t>skincare_brand_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>brushes</t>
+          <t>k</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brushes</t>
+          <t>K</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>skincare_tools_choices</t>
+          <t>hair_haircut_size_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>less_than_100ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Less than 100ml</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>beard_tools_choices</t>
+          <t>hair_haircut_size_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>trimmers</t>
+          <t>100-200ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Trimmers</t>
+          <t>100-200ml</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>beard_tools_choices</t>
+          <t>hair_haircut_size_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>combs</t>
+          <t>more_than_200ml</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Combs</t>
+          <t>More than 200ml</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>beard_tools_choices</t>
+          <t>hair_haircut_form_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>brushes</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brushes</t>
+          <t>Pump</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>beard_tools_choices</t>
+          <t>hair_haircut_form_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>razors</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Razors</t>
+          <t>Bottle</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>beard_tools_choices</t>
+          <t>hair_haircut_form_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>tube</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Tube</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>skincare_brand_choices</t>
+          <t>skincare_size_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>less_than_100ml</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Less than 100ml</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>skincare_brand_choices</t>
+          <t>skincare_size_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>100-200ml</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>100-200ml</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>skincare_brand_choices</t>
+          <t>skincare_size_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>more_than_200ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>More than 200ml</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>skincare_brand_choices</t>
+          <t>skincare_size_form_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Pump</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>skincare_brand_choices</t>
+          <t>skincare_size_form_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bottle</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hair_haircut_brand_choices</t>
+          <t>skincare_size_form_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>tube</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Tube</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hair_haircut_brand_choices</t>
+          <t>skincare_product_size_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>10-20ml</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>10-20ml</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>hair_haircut_brand_choices</t>
+          <t>skincare_product_size_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>21-40ml</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>21-40ml</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hair_haircut_brand_choices</t>
+          <t>skincare_product_size_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>41-60ml</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>41-60ml</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>hair_haircut_brand_choices</t>
+          <t>skincare_product_form_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pump</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>skincare_haircut_choices</t>
+          <t>skincare_product_form_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Bottle</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>skincare_haircut_choices</t>
+          <t>skincare_product_form_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>tube</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Tube</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>skincare_haircut_choices</t>
+          <t>skincare_characteristics_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Cream</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>skincare_haircut_choices</t>
+          <t>skincare_characteristics_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>gel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Gel</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>skincare_characteristics_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Spray</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>skincare_characteristics_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1-2_times_a_week</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1-2 times a week</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>skincare_characteristics_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3-4_times_a_week</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3-4 times a week</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>hair_haircut_frequency_choices</t>
+          <t>skincare_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Cream</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>skincare_product_size_choices</t>
+          <t>skincare_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>less_than_100ml</t>
+          <t>gel</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Less than 100ml</t>
+          <t>Gel</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>skincare_product_size_choices</t>
+          <t>skincare_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>100-200ml</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>100-200ml</t>
+          <t>Spray</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>skincare_product_size_choices</t>
+          <t>skincare_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>more_than_200ml</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>More than 200ml</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>skincare_product_type_choices</t>
+          <t>skincare_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>skincare_product_type_choices</t>
+          <t>skincare_characteristics_3_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>gel</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cream</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>skincare_product_type_choices</t>
+          <t>skincare_characteristics_3_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>spray</t>
+          <t>gel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spray</t>
+          <t>Gel</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>skincare_product_type_choices</t>
+          <t>skincare_characteristics_3_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>serum</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Spray</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>skincare_product_type_choices</t>
+          <t>skincare_characteristics_3_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>skincare_product_form_choices</t>
+          <t>skincare_characteristics_3_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pump</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>skincare_product_form_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>bottle</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Bottle</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>skincare_product_form_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>tube</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Tube</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>skincare_product_form_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>tube</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Tube</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>skincare_product_form_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>skincare_product_size_form_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>10-20ml</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>10-20ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>skincare_product_size_form_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>21-40ml</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>21-40ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>skincare_product_size_form_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>41-60ml</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>41-60ml</t>
         </is>
       </c>
     </row>
